--- a/templates/INFRA ADV II SR - template.xlsx
+++ b/templates/INFRA ADV II SR - template.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20355" yWindow="-11640" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Email" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Email" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="DataAnálise">Email!$A$7</definedName>
@@ -1377,96 +1377,96 @@
     <row r="17" ht="15.95" customFormat="1" customHeight="1" s="34">
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
-        <v>1.040445361872</v>
+        <v>1.046105274873</v>
       </c>
       <c r="D17" s="37" t="n">
-        <v>0.0005426623900037786</v>
+        <v>0.0005426623344277903</v>
       </c>
       <c r="E17" s="37" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F17" s="38" t="n">
-        <v>1.000000055547736</v>
+        <v>0.9999999531341681</v>
       </c>
     </row>
     <row r="18" ht="15.95" customFormat="1" customHeight="1" s="34">
       <c r="B18" s="39" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
-        <v>1.039881057532</v>
+        <v>1.045537900835</v>
       </c>
       <c r="D18" s="41" t="n">
-        <v>0.0005426623617530435</v>
+        <v>0.0005426623942985653</v>
       </c>
       <c r="E18" s="41" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F18" s="42" t="n">
-        <v>1.000000003488228</v>
+        <v>1.000000063462025</v>
       </c>
     </row>
     <row r="19" ht="15.95" customFormat="1" customHeight="1" s="34">
       <c r="B19" s="39" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
-        <v>1.039317059282</v>
+        <v>1.04497083446</v>
       </c>
       <c r="D19" s="41" t="n">
-        <v>0.000542662351759482</v>
+        <v>0.0005426623825113275</v>
       </c>
       <c r="E19" s="41" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F19" s="42" t="n">
-        <v>0.9999999850724283</v>
+        <v>1.000000041740898</v>
       </c>
     </row>
     <row r="20" ht="15.95" customFormat="1" customHeight="1" s="34">
       <c r="B20" s="39" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C20" s="40" t="n">
-        <v>1.038753366937</v>
+        <v>1.044404075656</v>
       </c>
       <c r="D20" s="41" t="n">
-        <v>0.0005426623591859858</v>
+        <v>0.0005426622980393425</v>
       </c>
       <c r="E20" s="41" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F20" s="42" t="n">
-        <v>0.9999999987577406</v>
+        <v>0.9999998860787567</v>
       </c>
     </row>
     <row r="21" ht="15.95" customFormat="1" customHeight="1" s="34">
       <c r="B21" s="39" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C21" s="40" t="n">
-        <v>1.038189980313</v>
+        <v>1.043837624332</v>
       </c>
       <c r="D21" s="41" t="n">
-        <v>0.0005513106444898774</v>
+        <v>0.0005426624103028743</v>
       </c>
       <c r="E21" s="41" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F21" s="42" t="n">
-        <v>1.015936768918326</v>
+        <v>1.000000092954229</v>
       </c>
     </row>
     <row r="22" ht="15.95" customHeight="1">
@@ -1506,18 +1506,18 @@
     <row r="24" ht="15.95" customFormat="1" customHeight="1" s="34">
       <c r="B24" s="49" t="inlineStr">
         <is>
-          <t>Mar-26</t>
+          <t>Apr-26</t>
         </is>
       </c>
       <c r="C24" s="49" t="inlineStr"/>
       <c r="D24" s="41" t="n">
-        <v>0.01049210168863768</v>
+        <v>0.003804826240927595</v>
       </c>
       <c r="E24" s="41" t="n">
-        <v>0.01048336746569301</v>
+        <v>0.003804826246388782</v>
       </c>
       <c r="F24" s="42" t="n">
-        <v>1.000833150509439</v>
+        <v>0.9999999985646685</v>
       </c>
       <c r="G24" s="51" t="n"/>
     </row>
@@ -1530,13 +1530,13 @@
       </c>
       <c r="C25" s="49" t="inlineStr"/>
       <c r="D25" s="41" t="n">
-        <v>0.01160659892148463</v>
+        <v>0.0115191639536858</v>
       </c>
       <c r="E25" s="41" t="n">
-        <v>0.01159785506263344</v>
+        <v>0.0115104208368324</v>
       </c>
       <c r="F25" s="42" t="n">
-        <v>1.000753920341647</v>
+        <v>1.000759582727455</v>
       </c>
       <c r="G25" s="50" t="n"/>
     </row>
@@ -1549,13 +1549,13 @@
       </c>
       <c r="C26" s="49" t="inlineStr"/>
       <c r="D26" s="41" t="n">
-        <v>0.03529708620665417</v>
+        <v>0.0352076036320339</v>
       </c>
       <c r="E26" s="41" t="n">
-        <v>0.03528813776398843</v>
+        <v>0.03519865594435645</v>
       </c>
       <c r="F26" s="42" t="n">
-        <v>1.000253582173296</v>
+        <v>1.00025420537908</v>
       </c>
       <c r="G26" s="50" t="n"/>
     </row>
@@ -1568,13 +1568,13 @@
       </c>
       <c r="C27" s="49" t="inlineStr"/>
       <c r="D27" s="41" t="n">
-        <v>0.03244794886250046</v>
+        <v>0.03806435678046061</v>
       </c>
       <c r="E27" s="41" t="n">
-        <v>0.03243902489712824</v>
+        <v>0.0380553842733744</v>
       </c>
       <c r="F27" s="42" t="n">
-        <v>1.000275099680108</v>
+        <v>1.000235774970021</v>
       </c>
       <c r="G27" s="50" t="n"/>
     </row>
@@ -1606,13 +1606,13 @@
       </c>
       <c r="C29" s="49" t="inlineStr"/>
       <c r="D29" s="41" t="n">
-        <v>0.04044536187199999</v>
+        <v>0.04610527487299998</v>
       </c>
       <c r="E29" s="41" t="n">
-        <v>0.04043636873983614</v>
+        <v>0.0460962328228911</v>
       </c>
       <c r="F29" s="42" t="n">
-        <v>1.000222402071306</v>
+        <v>1.000196155944969</v>
       </c>
       <c r="G29" s="50" t="n"/>
     </row>
@@ -1640,7 +1640,7 @@
       <c r="C32" s="14" t="n"/>
       <c r="D32" s="14" t="n"/>
       <c r="E32" s="43" t="n">
-        <v>112409641.41</v>
+        <v>113021138</v>
       </c>
       <c r="F32" s="29" t="n"/>
       <c r="G32" s="4" t="n"/>
@@ -1655,7 +1655,7 @@
       <c r="C33" s="14" t="n"/>
       <c r="D33" s="14" t="n"/>
       <c r="E33" s="43" t="n">
-        <v>99936959.79219177</v>
+        <v>101480180.4007229</v>
       </c>
       <c r="F33" s="29" t="n"/>
       <c r="G33" s="4" t="n"/>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="C35" s="19" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="D35" s="20" t="n"/>
